--- a/upload/case-mix-2025.xlsx
+++ b/upload/case-mix-2025.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R3e07018dd2a34d28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rddb28201f88f480d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1491,6 +1491,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3092</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HEM</x:t>
         </x:is>
       </x:c>
@@ -2717,7 +2733,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.4998999999999998</x:v>
+        <x:v>1.6318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2733,7 +2749,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.5828</x:v>
+        <x:v>1.7183</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2749,7 +2765,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7683</x:v>
+        <x:v>1.8035</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2765,7 +2781,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6397</x:v>
+        <x:v>1.6264</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2781,7 +2797,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6199</x:v>
+        <x:v>1.6216</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2797,7 +2813,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7798</x:v>
+        <x:v>1.7706</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7886</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4029,7 +4061,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.8781</x:v>
+        <x:v>0.8773</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4045,7 +4077,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.89050000000000007</x:v>
+        <x:v>0.8776</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4061,7 +4093,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.9459</x:v>
+        <x:v>0.9689</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -4125,7 +4157,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.9225</x:v>
+        <x:v>0.9293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HIJPII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1403</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5149,7 +5197,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1499</x:v>
+        <x:v>1.1504</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5181,7 +5229,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.0785</x:v>
+        <x:v>1.078</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5197,7 +5245,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.0755</x:v>
+        <x:v>1.0757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5213,7 +5261,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2067</x:v>
+        <x:v>1.2097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5229,7 +5277,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1235</x:v>
+        <x:v>1.1244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5405,7 +5453,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1144</x:v>
+        <x:v>1.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5421,7 +5469,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1985</x:v>
+        <x:v>1.2048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5437,7 +5485,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1912</x:v>
+        <x:v>1.1918</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5453,7 +5501,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1695</x:v>
+        <x:v>1.169</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5469,7 +5517,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1614</x:v>
+        <x:v>1.1608</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -5485,7 +5533,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2042</x:v>
+        <x:v>1.2189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6685,7 +6749,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.4383</x:v>
+        <x:v>1.4985</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6701,7 +6765,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.5972</x:v>
+        <x:v>1.5985000000000003</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6717,7 +6781,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1976</x:v>
+        <x:v>1.3071000000000002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6733,7 +6797,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.4428</x:v>
+        <x:v>1.4439</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -6797,7 +6861,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6632</x:v>
+        <x:v>1.651</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.5497</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -7133,29 +7213,2845 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
+        <x:v>1.2275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3864</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2014</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2937</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2298</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3217</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.284</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.96379999999999988</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.0776</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.179</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.0859</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1546</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.0674</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1518</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1574</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1833</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.078</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2148</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.032</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.0803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1644</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2673</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3576</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3444</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.295</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2146</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2192</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.4132</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6296000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.4339</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2652</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.4533</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3997</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.251</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2807</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2095</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2223</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2697</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.5154999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2657</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2582</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.4424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3319</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3215</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.4823</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3943</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.4936999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6705</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.5677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.5706999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6073</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.576</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6979</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7019000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.1967</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.69</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.2656</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.3291</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6099</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2574</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3588</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9374</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3191999999999997</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8477000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6833</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.4282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.7424</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9239</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8746</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.1868</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6684000000000003</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8903</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7607000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.3299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.0569</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.5112</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7177</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.759</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9400000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1924</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.5229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9296</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.5997</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7376999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6283</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6888</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7524</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8827</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9222000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6717000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.0114</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7809</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6915</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8209</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9435</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.5913</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9018</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.5719</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9043</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8562999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7506</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.2259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.77</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8426999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7421</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6944</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7716</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7462</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9338000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6876</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.732</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.925</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.735</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6893</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.9579</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.6325999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7859</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>2.0067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8672</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8687999999999998</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.7289</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.5916</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.71369999999999989</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.4663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.7014</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.8839</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2885</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.97159999999999991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.598</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.8084</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.579</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.7758</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.0532</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.0923</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2737</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3653</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.1208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c s="9">
         <x:v>1.2372</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>HRAD</x:t>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.0697</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
         <x:v>2021</x:v>
       </x:c>
       <x:c s="8">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c s="8">
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3984</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1274</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7165,13 +10061,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2039</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.3996</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7181,13 +10077,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2944</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.2915</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7197,13 +10093,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2292</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.218</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7213,13 +10109,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3235</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.3959</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7229,13 +10125,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.284</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.5745000000000002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7245,13 +10141,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1142</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.3657</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7261,13 +10157,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.96379999999999988</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7277,13 +10173,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.0776</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.96130000000000015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7293,13 +10189,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.179</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.9498</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7309,13 +10205,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.0859</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7325,13 +10221,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1252</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7341,13 +10237,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1546</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.8416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7357,13 +10253,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.0674</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.8527</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7373,13 +10269,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1518</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.6592</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7389,13 +10285,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1574</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.9126</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7405,13 +10301,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1417</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.6814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7421,13 +10317,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2119</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.6902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7437,13 +10333,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1833</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.8351</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7453,13 +10349,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2625</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.8459000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7469,13 +10365,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.078</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.0476</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7485,13 +10381,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2148</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.9316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7501,13 +10397,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1067</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.6019</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7517,13 +10413,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1968</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.7033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7533,13 +10429,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.032</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.6817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7549,13 +10445,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.0803</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.6391</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7565,13 +10461,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1644</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.7265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7581,13 +10477,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2673</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.7677</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7597,13 +10493,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1984</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.6457</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7613,13 +10509,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3576</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.6025</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7629,13 +10525,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3444</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.3164</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7645,13 +10541,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.295</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.054</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7661,13 +10557,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2146</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7677,13 +10573,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2192</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.3501</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7693,13 +10589,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.376</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1942</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7709,13 +10605,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3195</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7725,13 +10621,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.4132</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.2528000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7741,13 +10637,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6296000000000002</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.2377</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7757,13 +10653,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.4339</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.0448</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7773,13 +10669,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2652</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7789,13 +10685,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.4533</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7805,13 +10701,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3997</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7821,13 +10717,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.251</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.2102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7837,13 +10733,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2807</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.2007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7853,13 +10749,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2095</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.2133</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7869,13 +10765,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2223</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.8585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7885,13 +10781,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2697</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1714</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7901,13 +10797,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1957</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.9482</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7917,13 +10813,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.5154999999999998</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.945</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7933,13 +10829,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2657</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.0746</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7949,13 +10845,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2908</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.1345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7965,13 +10861,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2582</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.9601</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7981,13 +10877,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3306</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.019</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -7997,13 +10893,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.4424</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.0889</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8013,13 +10909,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3319</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.0329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8029,13 +10925,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3215</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.0566</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8045,13 +10941,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.4823</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.0753</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8061,13 +10957,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3943</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.9141</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8077,13 +10973,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.4936999999999998</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.083</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8093,13 +10989,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6705</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.0169</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8109,13 +11005,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.5677</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.9335</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8125,13 +11021,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.5706999999999998</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.0778</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8141,13 +11037,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6073</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>0.9714</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8157,13 +11053,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.576</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.2238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8173,13 +11069,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6979</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.2373</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8189,13 +11085,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.622</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRAD</x:t>
+        <x:v>1.2481</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8205,13 +11101,29 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6997</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>1.102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.2876</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8221,13 +11133,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8256</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.6287</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8237,13 +11149,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.1967</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8253,13 +11165,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>0.69</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7142</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8269,13 +11181,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.2656</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.6043</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8285,13 +11197,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.3291</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8301,13 +11213,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9074</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.97710000000000008</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8317,13 +11229,29 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6099</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7818</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.8828</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8333,13 +11261,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2123</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8415</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8349,13 +11277,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2574</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>3.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8365,13 +11293,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.053</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.6365</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8381,13 +11309,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3588</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.6387</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8397,13 +11325,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9374</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.5884</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8413,13 +11341,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.3191999999999997</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8372</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8429,13 +11357,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8477000000000001</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.843</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8445,13 +11373,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6833</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8461,13 +11389,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6343</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8477,13 +11405,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.4282</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8493,13 +11421,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.7424</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7534</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8509,13 +11437,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9239</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8304</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8525,13 +11453,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8746</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8513</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8541,13 +11469,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.1868</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8536999999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8557,13 +11485,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6684000000000003</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.93080000000000007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8573,13 +11501,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8903</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8980999999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8589,13 +11517,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7607000000000002</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.88049999999999984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8605,13 +11533,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.3299</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.89779999999999993</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8621,13 +11549,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.0569</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.943</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8637,13 +11565,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.5112</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.87270000000000014</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8653,13 +11581,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7177</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.89249999999999985</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8669,13 +11597,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.759</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9071</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8685,13 +11613,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9400000000000002</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8701,13 +11629,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.1924</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7107</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8717,13 +11645,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.5229</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7861</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8733,13 +11661,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9296</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8339</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8749,13 +11677,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.5997</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8897</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8765,13 +11693,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7376999999999998</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8326</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8781,13 +11709,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6283</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.843</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8797,13 +11725,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6888</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.90830000000000011</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8813,13 +11741,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7524</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8829,13 +11757,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8827</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8845,13 +11773,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.52</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8107</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8861,13 +11789,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9222000000000001</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8741</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8877,13 +11805,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6541</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.86129999999999984</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8893,13 +11821,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6717000000000002</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7839</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8909,13 +11837,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.0114</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.84170000000000011</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8925,13 +11853,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7809</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.80769999999999986</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8941,13 +11869,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6915</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.90670000000000006</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8957,13 +11885,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8209</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8973,13 +11901,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9435</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.81120000000000014</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -8989,13 +11917,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.5913</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8501</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9005,13 +11933,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9622</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8327</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9021,13 +11949,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9908</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.90250000000000008</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9037,13 +11965,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9018</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8566</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9053,13 +11981,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.5719</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9282</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9069,13 +11997,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6618</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.86169999999999991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9085,13 +12013,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9043</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8575</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9101,13 +12029,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8562999999999998</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9355</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9117,13 +12045,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6854</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7962</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9133,13 +12061,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8065</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9348</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9149,13 +12077,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7506</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9649</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9165,13 +12093,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7563</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9181,13 +12109,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.2259</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.7752</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9197,13 +12125,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.77</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8249</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9213,13 +12141,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8426999999999998</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.91530000000000011</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9229,13 +12157,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8102</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.997</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9245,13 +12173,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7421</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>1.0399</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9261,13 +12189,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6944</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>1.0548</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9277,13 +12205,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6221</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9295</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9293,13 +12221,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7716</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.95120000000000016</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9309,13 +12237,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7462</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9246</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9325,13 +12253,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9338000000000002</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8574</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9341,13 +12269,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9272</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9357,13 +12285,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7902</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.89139999999999986</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9373,13 +12301,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6876</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9246</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9389,13 +12317,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7938</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9817999999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9405,13 +12333,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.732</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9102</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9421,13 +12349,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.925</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9437,13 +12365,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9413</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.837</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9453,13 +12381,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.735</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.97820000000000007</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9469,13 +12397,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6893</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9658000000000001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9485,13 +12413,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.9579</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8983</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9501,13 +12429,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.391</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9517,13 +12445,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.6476</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.9655999999999999</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9533,13 +12461,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.7354</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8674</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9549,13 +12477,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>2.0038</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8896</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9565,13 +12493,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8672</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRBJA</x:t>
+        <x:v>0.8784</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
@@ -9581,2807 +12509,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.8687999999999998</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.5916</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.71369999999999989</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.4663</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7014</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.8839</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
+        <x:v>0.9114</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
       </x:c>
       <x:c s="8">
         <x:v>9</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>1.2885</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.97159999999999991</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.598</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8084</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.579</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1053</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7758</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0532</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0923</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2737</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.3653</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1208</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.509</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2372</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0697</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2367</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1274</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.3996</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2915</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.218</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.3959</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.5745000000000002</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.3657</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1288</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.96130000000000015</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9498</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1983</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.047</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8416</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8527</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6592</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9126</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6814</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6902</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8351</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8459000000000001</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0476</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9316</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6019</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7033</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6817</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6391</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7265</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7677</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6457</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6025</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.3164</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.054</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1778</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.3501</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1942</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1995</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2528000000000001</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2377</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0448</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1088</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1704</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.335</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2102</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2007</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2133</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8585</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1714</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9482</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.945</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0746</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.1345</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9601</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.019</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0889</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0329</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0566</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0753</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9141</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.083</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0169</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9335</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0669</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9714</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2238</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2373</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.2481</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>HRJP</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0978</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6287</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9707</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7142</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6043</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8782</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.97710000000000008</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7818</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2019</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8828</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8415</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>3.6991</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6365</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.6387</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.5884</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8372</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.843</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7512</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7635</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8058</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2020</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7534</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8304</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8513</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8536999999999999</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.93080000000000007</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8980999999999999</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.88049999999999984</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.89779999999999993</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.943</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.87270000000000014</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.89249999999999985</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9071</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2021</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8033</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7107</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7861</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8339</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8897</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8326</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.843</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.90830000000000011</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8048</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7775</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8107</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8741</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.86129999999999984</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7839</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.84170000000000011</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.80769999999999986</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.90670000000000006</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8202</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.81120000000000014</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8501</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8327</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.90250000000000008</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8566</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9282</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2023</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.86169999999999991</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8575</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9355</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7962</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9348</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9649</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8681</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.7752</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8249</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.91530000000000011</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.997</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0399</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2024</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>1.0548</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9295</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.95120000000000016</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9246</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8574</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.911</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.89139999999999986</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9246</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9817999999999999</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9102</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8968</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.837</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2025</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.97820000000000007</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9658000000000001</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8983</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9345</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9655999999999999</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8674</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.8896</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.886</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>MOV</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c s="8">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.9114000000000001</x:v>
+        <x:v>0.9467</x:v>
       </x:c>
     </x:row>
     <x:row/>
